--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DC6AEB-9577-438A-9F0F-B05DA17C8911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525F7A42-C923-4577-88AF-A624AB4ADCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="1950" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
   <si>
     <t>Category</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Content</t>
   </si>
   <si>
-    <t>Introduction to Agentic AI</t>
-  </si>
-  <si>
     <t>What is Agentic AI</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>Differences between rule-based bots, LLM chatbots, and autonomous agents</t>
   </si>
   <si>
-    <t>Core Concepts</t>
-  </si>
-  <si>
     <t>Components of an AI Agent</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>How LLM works as reasoning engine, prompts as instructions</t>
   </si>
   <si>
-    <t>Tools in Agents</t>
-  </si>
-  <si>
     <t>What are tools, APIs, function calling, examples (calculator, search, DB query)</t>
   </si>
   <si>
@@ -99,9 +90,6 @@
     <t>How agents perceive and act in environments, input-output loop</t>
   </si>
   <si>
-    <t>Prompt Engineering for Agents</t>
-  </si>
-  <si>
     <t>Prompt Design for Agents</t>
   </si>
   <si>
@@ -120,9 +108,6 @@
     <t>Examples for guiding agent behavior</t>
   </si>
   <si>
-    <t>Agent Architectures</t>
-  </si>
-  <si>
     <t>ReAct Architecture</t>
   </si>
   <si>
@@ -144,9 +129,6 @@
     <t>Self-improving agents, feedback loops</t>
   </si>
   <si>
-    <t>Tools &amp; Frameworks</t>
-  </si>
-  <si>
     <t>LangChain Basics</t>
   </si>
   <si>
@@ -174,9 +156,6 @@
     <t>How agents call APIs/functions dynamically</t>
   </si>
   <si>
-    <t>Hands-on Implementation</t>
-  </si>
-  <si>
     <t>Build Simple Agent (Python)</t>
   </si>
   <si>
@@ -279,9 +258,6 @@
     <t>pdf+code done</t>
   </si>
   <si>
-    <t>pdf done seperately</t>
-  </si>
-  <si>
     <t>Simple agent with tools (calculator/weather API) -&gt; to streamlit</t>
   </si>
   <si>
@@ -295,13 +271,67 @@
   </si>
   <si>
     <t>Email, scheduling, or file processing agent (- POC)</t>
+  </si>
+  <si>
+    <t>pdf doone</t>
+  </si>
+  <si>
+    <t>pf done</t>
+  </si>
+  <si>
+    <t>pdf done with above</t>
+  </si>
+  <si>
+    <t>pdf done- Review it</t>
+  </si>
+  <si>
+    <t>Tools in Agents + Executor</t>
+  </si>
+  <si>
+    <t>1 Introduction to Agentic AI</t>
+  </si>
+  <si>
+    <t>2 Core Concepts</t>
+  </si>
+  <si>
+    <t>3 Prompt Engineering for Agents</t>
+  </si>
+  <si>
+    <t>4  Agent Architectures</t>
+  </si>
+  <si>
+    <t>5 Tools &amp; Frameworks</t>
+  </si>
+  <si>
+    <t>Done in  module 4</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Tool calling agent</t>
+  </si>
+  <si>
+    <t>Code generation  + execution</t>
+  </si>
+  <si>
+    <t>code done</t>
+  </si>
+  <si>
+    <t>pdf + code done ??? Remove this</t>
+  </si>
+  <si>
+    <t>pdf + code done - Verify</t>
+  </si>
+  <si>
+    <t>6 Hands-on Implementation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +343,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -338,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -346,6 +382,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,14 +666,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="31" style="3" customWidth="1"/>
     <col min="4" max="4" width="98.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -651,538 +690,577 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3">
         <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
+      <c r="E3" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
+      <c r="E4" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="3">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3">
-        <v>30</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="B7" s="3">
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3">
         <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3">
         <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3">
         <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3">
         <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="B13" s="3">
         <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="3">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" s="3">
-        <v>30</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="B15" s="3">
         <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B17" s="3">
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B18" s="3">
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B19" s="3">
         <v>25</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B20" s="3">
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="3">
-        <v>30</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>82</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B23" s="3">
         <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B24" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>77</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B25" s="3">
         <v>25</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="3">
+        <v>25</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3">
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="3">
-        <v>30</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>87</v>
+      <c r="C27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="B29" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>78</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="B30" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="B31" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="3">
+        <v>35</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="3">
-        <v>30</v>
-      </c>
-      <c r="C32" s="3" t="s">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="3">
+        <v>30</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="3">
+        <v>30</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="3">
+        <v>25</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="3">
+        <v>30</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" t="s">
         <v>57</v>
       </c>
-      <c r="D32" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="3">
+        <v>25</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="3">
-        <v>30</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="D38" t="s">
         <v>59</v>
       </c>
-      <c r="D34" t="s">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="3">
-        <v>25</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B40" s="3">
+        <v>30</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D40" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="3">
-        <v>30</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="3">
-        <v>25</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="3">
-        <v>30</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="3">
-        <v>25</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B41" s="3">
         <v>25</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="3">
+        <v>25</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="3">
+        <v>60</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="3">
+        <v>30</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="3">
+        <v>20</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D46" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" s="3">
-        <v>60</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" s="3">
-        <v>30</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" s="3">
-        <v>20</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D45" t="s">
-        <v>80</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525F7A42-C923-4577-88AF-A624AB4ADCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CE71AD-F9B9-4C49-91B3-4B76BDBB89E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1950" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1455" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CE71AD-F9B9-4C49-91B3-4B76BDBB89E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5362F3C-524E-48B2-9EF6-854C56620B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1455" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1065" yWindow="1800" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="103">
   <si>
     <t>Category</t>
   </si>
@@ -325,6 +325,15 @@
   </si>
   <si>
     <t>6 Hands-on Implementation</t>
+  </si>
+  <si>
+    <t>misc</t>
+  </si>
+  <si>
+    <t>How to connect to google drive</t>
+  </si>
+  <si>
+    <t>WIP</t>
   </si>
 </sst>
 </file>
@@ -666,12 +675,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="31" style="3" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="98.5703125" customWidth="1"/>
     <col min="5" max="5" width="37" customWidth="1"/>
   </cols>
@@ -1259,6 +1268,17 @@
         <v>73</v>
       </c>
     </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5362F3C-524E-48B2-9EF6-854C56620B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B2DF11-7D3F-4878-931A-DC2551F42000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="1800" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
   <si>
     <t>Category</t>
   </si>
@@ -334,6 +334,15 @@
   </si>
   <si>
     <t>WIP</t>
+  </si>
+  <si>
+    <t>6 Hands-on Implementation-EXTRA</t>
+  </si>
+  <si>
+    <t>NL to SQL</t>
+  </si>
+  <si>
+    <t>Converts NL to SQL and retrieves data from  DB</t>
   </si>
 </sst>
 </file>
@@ -675,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -1128,18 +1137,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="3">
-        <v>30</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" t="s">
-        <v>53</v>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1147,13 +1156,13 @@
         <v>51</v>
       </c>
       <c r="B36" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1161,13 +1170,13 @@
         <v>51</v>
       </c>
       <c r="B37" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1175,27 +1184,27 @@
         <v>51</v>
       </c>
       <c r="B38" s="3">
+        <v>30</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="3">
         <v>25</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="3">
-        <v>30</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1203,13 +1212,13 @@
         <v>60</v>
       </c>
       <c r="B41" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1220,24 +1229,24 @@
         <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="3">
+        <v>25</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="3">
-        <v>60</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D44" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1245,13 +1254,13 @@
         <v>67</v>
       </c>
       <c r="B45" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1259,23 +1268,37 @@
         <v>67</v>
       </c>
       <c r="B46" s="3">
+        <v>30</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="3">
         <v>20</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>102</v>
       </c>
     </row>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B2DF11-7D3F-4878-931A-DC2551F42000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919552EF-E1F8-4737-990D-C143317761F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
   <si>
     <t>Category</t>
   </si>
@@ -312,9 +312,6 @@
     <t>Tool calling agent</t>
   </si>
   <si>
-    <t>Code generation  + execution</t>
-  </si>
-  <si>
     <t>code done</t>
   </si>
   <si>
@@ -343,6 +340,15 @@
   </si>
   <si>
     <t>Converts NL to SQL and retrieves data from  DB</t>
+  </si>
+  <si>
+    <t>Project in  finance domain- nl2sql2report</t>
+  </si>
+  <si>
+    <t>Code generation  +     execution</t>
+  </si>
+  <si>
+    <t>pdf  +   code done</t>
   </si>
 </sst>
 </file>
@@ -684,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -917,7 +923,7 @@
         <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,51 +961,45 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="3">
-        <v>20</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>105</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="3">
+        <v>20</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="3">
-        <v>30</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1010,13 +1010,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1024,13 +1024,16 @@
         <v>91</v>
       </c>
       <c r="B25" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1041,10 +1044,10 @@
         <v>25</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1052,117 +1055,117 @@
         <v>91</v>
       </c>
       <c r="B27" s="3">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="3">
         <v>20</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="3">
-        <v>30</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B30" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>78</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B32" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="3">
+        <v>30</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D35" t="s">
         <v>104</v>
       </c>
-      <c r="D34" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="3">
-        <v>30</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1170,13 +1173,13 @@
         <v>51</v>
       </c>
       <c r="B37" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1184,13 +1187,13 @@
         <v>51</v>
       </c>
       <c r="B38" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1198,27 +1201,27 @@
         <v>51</v>
       </c>
       <c r="B39" s="3">
+        <v>30</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="3">
         <v>25</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="3">
-        <v>30</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1226,13 +1229,13 @@
         <v>60</v>
       </c>
       <c r="B42" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1243,24 +1246,24 @@
         <v>25</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="3">
+        <v>25</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="3">
-        <v>60</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D45" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1268,13 +1271,13 @@
         <v>67</v>
       </c>
       <c r="B46" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1282,24 +1285,38 @@
         <v>67</v>
       </c>
       <c r="B47" s="3">
+        <v>30</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="3">
         <v>20</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D50" t="s">
         <v>101</v>
-      </c>
-      <c r="D49" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919552EF-E1F8-4737-990D-C143317761F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2F705D-F3AE-49EC-8BD1-7511E4D05919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="2730" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="107">
   <si>
     <t>Category</t>
   </si>
@@ -312,9 +312,6 @@
     <t>Tool calling agent</t>
   </si>
   <si>
-    <t>code done</t>
-  </si>
-  <si>
     <t>pdf + code done ??? Remove this</t>
   </si>
   <si>
@@ -345,10 +342,10 @@
     <t>Project in  finance domain- nl2sql2report</t>
   </si>
   <si>
-    <t>Code generation  +     execution</t>
-  </si>
-  <si>
     <t>pdf  +   code done</t>
+  </si>
+  <si>
+    <t>Code generation  +     execution : Single Agent ReAct Based</t>
   </si>
 </sst>
 </file>
@@ -690,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -923,7 +920,7 @@
         <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -965,7 +962,7 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>79</v>
@@ -999,25 +996,12 @@
         <v>106</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="3">
-        <v>30</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>75</v>
-      </c>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -1027,13 +1011,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1041,13 +1025,16 @@
         <v>91</v>
       </c>
       <c r="B26" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>77</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1058,10 +1045,10 @@
         <v>25</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1069,132 +1056,121 @@
         <v>91</v>
       </c>
       <c r="B28" s="3">
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="3">
-        <v>30</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B31" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>78</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B33" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="3">
+        <v>30</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D36" t="s">
         <v>103</v>
       </c>
-      <c r="D35" t="s">
-        <v>104</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="3">
-        <v>30</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3">
-        <v>25</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" t="s">
-        <v>55</v>
-      </c>
+      <c r="E37" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -1204,10 +1180,10 @@
         <v>30</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1218,38 +1194,38 @@
         <v>25</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="3">
+        <v>30</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B42" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="3">
-        <v>25</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1257,41 +1233,41 @@
         <v>60</v>
       </c>
       <c r="B44" s="3">
+        <v>30</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="3">
         <v>25</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" t="s">
-        <v>66</v>
+      <c r="C45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B46" s="3">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B47" s="3">
-        <v>30</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1299,24 +1275,52 @@
         <v>67</v>
       </c>
       <c r="B48" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="3">
+        <v>30</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="3">
+        <v>20</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D52" t="s">
         <v>100</v>
-      </c>
-      <c r="D50" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2F705D-F3AE-49EC-8BD1-7511E4D05919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2F7678-A711-4802-B155-F73F379662E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="2730" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="108">
   <si>
     <t>Category</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>Code generation  +     execution : Single Agent ReAct Based</t>
+  </si>
+  <si>
+    <t>email agent</t>
   </si>
 </sst>
 </file>
@@ -687,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -1170,34 +1173,31 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="3"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="3">
-        <v>30</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" t="s">
-        <v>53</v>
-      </c>
+      <c r="A37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1205,13 +1205,13 @@
         <v>51</v>
       </c>
       <c r="B41" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1219,27 +1219,27 @@
         <v>51</v>
       </c>
       <c r="B42" s="3">
+        <v>30</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="3">
         <v>25</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" s="3">
-        <v>30</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1247,13 +1247,13 @@
         <v>60</v>
       </c>
       <c r="B45" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1264,24 +1264,24 @@
         <v>25</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="3">
+        <v>25</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48" s="3">
-        <v>60</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1289,13 +1289,13 @@
         <v>67</v>
       </c>
       <c r="B49" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,23 +1303,37 @@
         <v>67</v>
       </c>
       <c r="B50" s="3">
+        <v>30</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="3">
         <v>20</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>100</v>
       </c>
     </row>
